--- a/REPORTING MODULE/Doctor List-Alfez.xlsx
+++ b/REPORTING MODULE/Doctor List-Alfez.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DESKTOP FILES\WEEKLY RVW\DR'S LIST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MY WORK FLOW\Emyris Onboard App\REPORTING MODULE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B11C0AE-DEC5-466B-BF9C-8EC331FC3F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C0B956-054B-4BFE-8B40-7403E2F96931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="384">
   <si>
     <t>Sr</t>
   </si>
@@ -96,18 +96,12 @@
     <t>-</t>
   </si>
   <si>
-    <t>DOC663</t>
-  </si>
-  <si>
     <t>samanvay hospital vadodara</t>
   </si>
   <si>
     <t>SuperCore (3 Visits/Month)</t>
   </si>
   <si>
-    <t>DOC740</t>
-  </si>
-  <si>
     <t>vadodara</t>
   </si>
   <si>
@@ -123,30 +117,18 @@
     <t>Physician</t>
   </si>
   <si>
-    <t>DOC642</t>
-  </si>
-  <si>
     <t>Nirvana hospital vadodara</t>
   </si>
   <si>
-    <t>DOC736</t>
-  </si>
-  <si>
     <t>Dr Manoj Mehta</t>
   </si>
   <si>
     <t>MD</t>
   </si>
   <si>
-    <t>DOC659</t>
-  </si>
-  <si>
     <t>sterling hospital vadodara near Inox</t>
   </si>
   <si>
-    <t>DOC741</t>
-  </si>
-  <si>
     <t>Smit Bhavsar</t>
   </si>
   <si>
@@ -156,45 +138,27 @@
     <t>Intensivist</t>
   </si>
   <si>
-    <t>DOC648</t>
-  </si>
-  <si>
     <t>Shroff foundation vadodara</t>
   </si>
   <si>
-    <t>DOC738</t>
-  </si>
-  <si>
     <t>mansi  shah</t>
   </si>
   <si>
     <t>7016420587</t>
   </si>
   <si>
-    <t>DOC713</t>
-  </si>
-  <si>
     <t>gujrat kidney hospital</t>
   </si>
   <si>
     <t>Non-Core (1 Visit/Month)</t>
   </si>
   <si>
-    <t>DOC760</t>
-  </si>
-  <si>
     <t>Raviraj Gohil</t>
   </si>
   <si>
-    <t>DOC666</t>
-  </si>
-  <si>
     <t>adicura hospital vadodara</t>
   </si>
   <si>
-    <t>DOC755</t>
-  </si>
-  <si>
     <t>Mehul Agrawat</t>
   </si>
   <si>
@@ -204,18 +168,12 @@
     <t>Gastroenterology</t>
   </si>
   <si>
-    <t>DOC656</t>
-  </si>
-  <si>
     <t>svasthya hospital vadodara</t>
   </si>
   <si>
     <t>Core (2 Visits/Month)</t>
   </si>
   <si>
-    <t>DOC749</t>
-  </si>
-  <si>
     <t>Yogesh Bhargav</t>
   </si>
   <si>
@@ -225,54 +183,30 @@
     <t>Nephrologist</t>
   </si>
   <si>
-    <t>DOC662</t>
-  </si>
-  <si>
     <t>premier kidney hospital vadodara</t>
   </si>
   <si>
-    <t>DOC756</t>
-  </si>
-  <si>
     <t>Fenil Majumdar</t>
   </si>
   <si>
-    <t>DOC714</t>
-  </si>
-  <si>
     <t xml:space="preserve">kalpvruksh hospital &amp; ICU vadodara </t>
   </si>
   <si>
-    <t>DOC762</t>
-  </si>
-  <si>
     <t>Purvesh Umarania</t>
   </si>
   <si>
-    <t>DOC653</t>
-  </si>
-  <si>
     <t>bhailal Amin hospital vadodara</t>
   </si>
   <si>
-    <t>DOC747</t>
-  </si>
-  <si>
     <t>Arjun Joshi ( Icon Plus)</t>
   </si>
   <si>
     <t>IDCCM</t>
   </si>
   <si>
-    <t>DOC646</t>
-  </si>
-  <si>
     <t>icon plus hospital vadodara</t>
   </si>
   <si>
-    <t>DOC743</t>
-  </si>
-  <si>
     <t>Amit Doshi</t>
   </si>
   <si>
@@ -282,72 +216,39 @@
     <t>Urologist</t>
   </si>
   <si>
-    <t>DOC698</t>
-  </si>
-  <si>
     <t>Sankalp hospital vadodara</t>
   </si>
   <si>
-    <t>DOC757</t>
-  </si>
-  <si>
     <t xml:space="preserve">Parag Rana </t>
   </si>
   <si>
-    <t>DOC709</t>
-  </si>
-  <si>
     <t>dev medical hospital</t>
   </si>
   <si>
-    <t>DOC759</t>
-  </si>
-  <si>
     <t>Tyron Farnandis</t>
   </si>
   <si>
-    <t>DOC702</t>
-  </si>
-  <si>
     <t>zydus hospital vadodara</t>
   </si>
   <si>
-    <t>DOC761</t>
-  </si>
-  <si>
     <t>Misbah Rangwala</t>
   </si>
   <si>
-    <t>DOC680</t>
-  </si>
-  <si>
     <t>parul sevashram hospital vadodara</t>
   </si>
   <si>
-    <t>DOC750</t>
-  </si>
-  <si>
     <t>Aman Khanna</t>
   </si>
   <si>
     <t>anjna hospital vadodara</t>
   </si>
   <si>
-    <t>DOC782</t>
-  </si>
-  <si>
     <t>Gorang Patel</t>
   </si>
   <si>
-    <t>DOC711</t>
-  </si>
-  <si>
     <t>Baroda lifeline hospital</t>
   </si>
   <si>
-    <t>DOC781</t>
-  </si>
-  <si>
     <t>Himanshu Nayak</t>
   </si>
   <si>
@@ -357,15 +258,9 @@
     <t>Plastic Surgeon</t>
   </si>
   <si>
-    <t>DOC722</t>
-  </si>
-  <si>
     <t>naik super speciality hospital vadodara</t>
   </si>
   <si>
-    <t>DOC765</t>
-  </si>
-  <si>
     <t>Vibha Nayak</t>
   </si>
   <si>
@@ -375,159 +270,81 @@
     <t>Oncology</t>
   </si>
   <si>
-    <t>DOC724</t>
-  </si>
-  <si>
-    <t>DOC767</t>
-  </si>
-  <si>
     <t>Mosam Shah</t>
   </si>
   <si>
-    <t>DOC661</t>
-  </si>
-  <si>
     <t>monal hospital vadodara</t>
   </si>
   <si>
-    <t>DOC784</t>
-  </si>
-  <si>
     <t>Ishaq Bhana</t>
   </si>
   <si>
-    <t>DOC717</t>
-  </si>
-  <si>
     <t>bhana hospital vadodara</t>
   </si>
   <si>
-    <t>DOC764</t>
-  </si>
-  <si>
     <t>Niraj Bhatt</t>
   </si>
   <si>
-    <t>DOC664</t>
-  </si>
-  <si>
     <t>hemato oncology clinic vadodara doctor house</t>
   </si>
   <si>
-    <t>DOC778</t>
-  </si>
-  <si>
     <t>Karsishma Matai</t>
   </si>
   <si>
-    <t>DOC716</t>
-  </si>
-  <si>
     <t>sterling hospital near Inox vadodara</t>
   </si>
   <si>
-    <t>DOC763</t>
-  </si>
-  <si>
     <t>Mani Bapna</t>
   </si>
   <si>
-    <t>DOC726</t>
-  </si>
-  <si>
     <t>manav hospital &amp; ICU vadodara</t>
   </si>
   <si>
-    <t>DOC768</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jayesh Rajpura </t>
   </si>
   <si>
-    <t>DOC718</t>
-  </si>
-  <si>
     <t>siddhi ICU hospital vadodara</t>
   </si>
   <si>
-    <t>DOC771</t>
-  </si>
-  <si>
     <t>Arif Kesrani</t>
   </si>
   <si>
     <t xml:space="preserve">MD </t>
   </si>
   <si>
-    <t>DOC682</t>
-  </si>
-  <si>
     <t>khadim hospital vadodara</t>
   </si>
   <si>
-    <t>DOC785</t>
-  </si>
-  <si>
     <t>Tushar Patel</t>
   </si>
   <si>
-    <t>DOC721</t>
-  </si>
-  <si>
     <t>sukan hospital vadodara</t>
   </si>
   <si>
-    <t>DOC769</t>
-  </si>
-  <si>
     <t>Amit Dave</t>
   </si>
   <si>
-    <t>DOC689</t>
-  </si>
-  <si>
     <t>Daya madhav hospital vadodara</t>
   </si>
   <si>
-    <t>DOC789</t>
-  </si>
-  <si>
     <t>Ankur Bhavsar</t>
   </si>
   <si>
-    <t>DOC692</t>
-  </si>
-  <si>
     <t>spandan hospital vadodara</t>
   </si>
   <si>
-    <t>DOC792</t>
-  </si>
-  <si>
     <t>Pranav Patel</t>
   </si>
   <si>
-    <t>DOC690</t>
-  </si>
-  <si>
     <t>HCG oncology vadodara</t>
   </si>
   <si>
-    <t>DOC786</t>
-  </si>
-  <si>
     <t>Udgeet Thakkar</t>
   </si>
   <si>
-    <t>DOC671</t>
-  </si>
-  <si>
     <t>secure hospital vadodara</t>
   </si>
   <si>
-    <t>DOC791</t>
-  </si>
-  <si>
     <t>Divya Pavithran</t>
   </si>
   <si>
@@ -537,36 +354,18 @@
     <t>Dietitians</t>
   </si>
   <si>
-    <t>DOC715</t>
-  </si>
-  <si>
     <t>pranayam hospital vadodara</t>
   </si>
   <si>
-    <t>DOC796</t>
-  </si>
-  <si>
     <t>Ashish Bavisi</t>
   </si>
   <si>
-    <t>DOC699</t>
-  </si>
-  <si>
     <t>vitas hospital vadodara</t>
   </si>
   <si>
-    <t>DOC795</t>
-  </si>
-  <si>
     <t>Ashish Soneji</t>
   </si>
   <si>
-    <t>DOC704</t>
-  </si>
-  <si>
-    <t>DOC798</t>
-  </si>
-  <si>
     <t>Neel Thakkar</t>
   </si>
   <si>
@@ -576,189 +375,93 @@
     <t>Pulmonology</t>
   </si>
   <si>
-    <t>DOC688</t>
-  </si>
-  <si>
-    <t>DOC793</t>
-  </si>
-  <si>
     <t>Tejas Kakkad</t>
   </si>
   <si>
-    <t>DOC673</t>
-  </si>
-  <si>
     <t xml:space="preserve">breathwell chest hospital vadodara </t>
   </si>
   <si>
-    <t>DOC805</t>
-  </si>
-  <si>
     <t>Mubarak Patel</t>
   </si>
   <si>
-    <t>DOC677</t>
-  </si>
-  <si>
     <t>harmony hospital vadodara</t>
   </si>
   <si>
-    <t>DOC797</t>
-  </si>
-  <si>
     <t>Hetal Shah</t>
   </si>
   <si>
-    <t>DOC665</t>
-  </si>
-  <si>
-    <t>DOC803</t>
-  </si>
-  <si>
     <t>Dhrumit Gohil</t>
   </si>
   <si>
-    <t>DOC686</t>
-  </si>
-  <si>
     <t>Synergy medicare hospital vadodara</t>
   </si>
   <si>
-    <t>DOC802</t>
-  </si>
-  <si>
     <t>Revathi Aiyer</t>
   </si>
   <si>
-    <t>DOC657</t>
-  </si>
-  <si>
-    <t>DOC804</t>
-  </si>
-  <si>
     <t>Archit Patel</t>
   </si>
   <si>
-    <t>DOC706</t>
-  </si>
-  <si>
     <t>vedanta kidney care hospital vadodara</t>
   </si>
   <si>
-    <t>DOC794</t>
-  </si>
-  <si>
     <t>Chirag Rathod</t>
   </si>
   <si>
-    <t>DOC645</t>
-  </si>
-  <si>
     <t xml:space="preserve">samanvay hospital vadodara </t>
   </si>
   <si>
-    <t>DOC807</t>
-  </si>
-  <si>
     <t>dr vivek sharma</t>
   </si>
   <si>
-    <t>DOC899</t>
-  </si>
-  <si>
     <t xml:space="preserve">Shree Neelkanth Hospital waghodia road </t>
   </si>
   <si>
-    <t>DOC811</t>
-  </si>
-  <si>
     <t>sameer vaniyawala</t>
   </si>
   <si>
-    <t>DOC889</t>
-  </si>
-  <si>
     <t>moin clinic vadodara near panigate</t>
   </si>
   <si>
-    <t>DOC809</t>
-  </si>
-  <si>
     <t>Amit Chohan</t>
   </si>
   <si>
-    <t>DOC647</t>
-  </si>
-  <si>
     <t xml:space="preserve">sunshine hospital vadodara </t>
   </si>
   <si>
-    <t>DOC801</t>
-  </si>
-  <si>
     <t>Ashutosh Bhavsar</t>
   </si>
   <si>
-    <t>DOC643</t>
-  </si>
-  <si>
-    <t>DOC806</t>
-  </si>
-  <si>
     <t>dr manoj makwana</t>
   </si>
   <si>
-    <t>DOC897</t>
-  </si>
-  <si>
     <t>Sunrise hospital padra 391440</t>
   </si>
   <si>
-    <t>DOC810</t>
-  </si>
-  <si>
     <t>dr neha patel</t>
   </si>
   <si>
-    <t>DOC10</t>
-  </si>
-  <si>
     <t xml:space="preserve">A-209,2nd Floor,EmeraldOne, Opp. Swadia Hospital jetalpur Road, Vadodara </t>
   </si>
   <si>
-    <t>DOC817</t>
-  </si>
-  <si>
     <t>hardik gajera</t>
   </si>
   <si>
     <t>Nephrology</t>
   </si>
   <si>
-    <t>DOC942</t>
-  </si>
-  <si>
     <t xml:space="preserve">Shroff foundation vadodara </t>
   </si>
   <si>
-    <t>DOC826</t>
-  </si>
-  <si>
     <t>piyusha chandrayan</t>
   </si>
   <si>
     <t>Gynecology</t>
   </si>
   <si>
-    <t>DOC74</t>
-  </si>
-  <si>
     <t>Second floor, Pancham Icon, New VIP Rd, nr. Bank Of Baroda, Sardar Estate, Sayaji Park Society, Vadodara, Gujarat 390019</t>
   </si>
   <si>
-    <t>DOC828</t>
-  </si>
-  <si>
     <t>sonia dalal</t>
   </si>
   <si>
@@ -768,132 +471,72 @@
     <t>Chest</t>
   </si>
   <si>
-    <t>DOC54</t>
-  </si>
-  <si>
     <t>101-102, Shree Hari Corner, Anand Society, B/H Express Hotel, Alkapuri, Vadodara, Gujarat 390007</t>
   </si>
   <si>
-    <t>DOC813</t>
-  </si>
-  <si>
     <t>archana dwivedi</t>
   </si>
   <si>
-    <t>DOC175</t>
-  </si>
-  <si>
     <t>Sterling hospital vadodara near Inox</t>
   </si>
   <si>
-    <t>DOC820</t>
-  </si>
-  <si>
     <t>deepak mohapatra</t>
   </si>
   <si>
     <t>CIP</t>
   </si>
   <si>
-    <t>DOC178</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sterling hospital vadodara </t>
   </si>
   <si>
-    <t>DOC822</t>
-  </si>
-  <si>
     <t>preeti thakor</t>
   </si>
   <si>
-    <t>DOC188</t>
-  </si>
-  <si>
     <t>Gayatri Maternity &amp; I.V.F Centre vadodara</t>
   </si>
   <si>
-    <t>DOC824</t>
-  </si>
-  <si>
     <t>shilpi shukla</t>
   </si>
   <si>
     <t>MD, MBBS</t>
   </si>
   <si>
-    <t>DOC176</t>
-  </si>
-  <si>
     <t>Isha hospital vadodara</t>
   </si>
   <si>
-    <t>DOC819</t>
-  </si>
-  <si>
     <t>ankur tiwari</t>
   </si>
   <si>
-    <t>DOC969</t>
-  </si>
-  <si>
-    <t>DOC827</t>
-  </si>
-  <si>
     <t>rajesh kantharia</t>
   </si>
   <si>
     <t>MD, MS</t>
   </si>
   <si>
-    <t>DOC974</t>
-  </si>
-  <si>
     <t>BANKERS SUPERSPECIALITY HOSPITAL GIDC Rd, opposite MAHALAXMI PARTY PLOT TULSIDHAM, Manjalpur, Vadodara, Gujarat 390011</t>
   </si>
   <si>
-    <t>DOC831</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Mayur Jadhav</t>
   </si>
   <si>
-    <t>DOC883</t>
-  </si>
-  <si>
     <t>bankers heart institute vadodara</t>
   </si>
   <si>
-    <t>DOC832</t>
-  </si>
-  <si>
     <t>vibhav parghi</t>
   </si>
   <si>
     <t>Endocrinology</t>
   </si>
   <si>
-    <t>DOC918</t>
-  </si>
-  <si>
     <t>vadodara diabetes &amp; endocrine canter</t>
   </si>
   <si>
-    <t>DOC818</t>
-  </si>
-  <si>
     <t>saket kumar</t>
   </si>
   <si>
-    <t>DOC191</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sterling hospital vadodara bhayli </t>
   </si>
   <si>
-    <t>DOC825</t>
-  </si>
-  <si>
     <t>isha patel</t>
   </si>
   <si>
@@ -903,60 +546,30 @@
     <t>Deitician</t>
   </si>
   <si>
-    <t>DOC972</t>
-  </si>
-  <si>
     <t>Shroff foundation trust 7557+2CR, Kalali-Talsat Rd, Kalali, Vadodara, Gujarat 390012</t>
   </si>
   <si>
-    <t>DOC830</t>
-  </si>
-  <si>
     <t>dr mohini dietician</t>
   </si>
   <si>
-    <t>DOC177</t>
-  </si>
-  <si>
-    <t>DOC821</t>
-  </si>
-  <si>
     <t>Soham Gohil</t>
   </si>
   <si>
-    <t>DOC683</t>
-  </si>
-  <si>
     <t>radiance urology hospital vadodara</t>
   </si>
   <si>
-    <t>DOC834</t>
-  </si>
-  <si>
     <t>Punit Ghetiya</t>
   </si>
   <si>
-    <t>DOC712</t>
-  </si>
-  <si>
     <t>banker heart institute vadodara</t>
   </si>
   <si>
-    <t>DOC835</t>
-  </si>
-  <si>
     <t>Divyesh Patel</t>
   </si>
   <si>
-    <t>DOC674</t>
-  </si>
-  <si>
     <t>tricolour hospital vadodara</t>
   </si>
   <si>
-    <t>DOC745</t>
-  </si>
-  <si>
     <t>dr ajay valia</t>
   </si>
   <si>
@@ -966,15 +579,9 @@
     <t>9227845964</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>Sarabhai Campus Sarabhai Main Road Behind, Atlantis Ln, Vadodara, Gujarat 390007</t>
   </si>
   <si>
-    <t>DOC1041</t>
-  </si>
-  <si>
     <t>2656507128</t>
   </si>
   <si>
@@ -987,9 +594,6 @@
     <t>109-118, 1ST FLOOR, RK PLAZA NR. UTKARSH SCHOOL, Diwalipura, Vadodara, Gujarat 390021</t>
   </si>
   <si>
-    <t>DOC1042</t>
-  </si>
-  <si>
     <t>dr dipen agrawal</t>
   </si>
   <si>
@@ -999,9 +603,6 @@
     <t>Niramay Gastro &amp; Liver Care 4th Floor, Sharnam Enclave, Gorwa</t>
   </si>
   <si>
-    <t>DOC1043</t>
-  </si>
-  <si>
     <t>dr rajesh korant</t>
   </si>
   <si>
@@ -1011,9 +612,6 @@
     <t>4, Vinodbaug, Jetalpur Rd, near Railway Station, Anand Nagar, Alkapuri, Vadodara, Gujarat 390007</t>
   </si>
   <si>
-    <t>DOC1044</t>
-  </si>
-  <si>
     <t>dr lalit machhar</t>
   </si>
   <si>
@@ -1026,9 +624,6 @@
     <t>127, Arpan Complex, Near Hanuman Temple, Delux Cross Road, Nizampura-390002 (Near Hanuman Temple)</t>
   </si>
   <si>
-    <t>DOC1047</t>
-  </si>
-  <si>
     <t>dr. sameer contractor</t>
   </si>
   <si>
@@ -1038,9 +633,6 @@
     <t>9824593464</t>
   </si>
   <si>
-    <t>DOC1137</t>
-  </si>
-  <si>
     <t>dr. jasmin rachhadia</t>
   </si>
   <si>
@@ -1050,9 +642,6 @@
     <t xml:space="preserve">Medwin hospital &amp; ICU vadodara </t>
   </si>
   <si>
-    <t>DOC1138</t>
-  </si>
-  <si>
     <t>saman musana</t>
   </si>
   <si>
@@ -1062,9 +651,6 @@
     <t>9699363733</t>
   </si>
   <si>
-    <t>DOC1250</t>
-  </si>
-  <si>
     <t>ankur prajapati</t>
   </si>
   <si>
@@ -1074,9 +660,6 @@
     <t xml:space="preserve">Baps hospital vadodara </t>
   </si>
   <si>
-    <t>DOC1260</t>
-  </si>
-  <si>
     <t>rahul thakkur</t>
   </si>
   <si>
@@ -1086,9 +669,6 @@
     <t>9978694108</t>
   </si>
   <si>
-    <t>DOC1261</t>
-  </si>
-  <si>
     <t>Maxillofacial Oncologist and Head Neck Surgeon</t>
   </si>
   <si>
@@ -1104,9 +684,6 @@
     <t xml:space="preserve">Vins hospital vadodara </t>
   </si>
   <si>
-    <t>DOC1262</t>
-  </si>
-  <si>
     <t xml:space="preserve">Neurosurgeon </t>
   </si>
   <si>
@@ -1122,9 +699,6 @@
     <t xml:space="preserve">Siddhi hospital &amp; icu vadodara </t>
   </si>
   <si>
-    <t>DOC1263</t>
-  </si>
-  <si>
     <t>sumeet kapadia</t>
   </si>
   <si>
@@ -1137,9 +711,6 @@
     <t>Adicura hospital vadodara</t>
   </si>
   <si>
-    <t>DOC1265</t>
-  </si>
-  <si>
     <t>Vascular surgeon</t>
   </si>
   <si>
@@ -1155,9 +726,6 @@
     <t>Gayatri Krupa Building, Sardar Bhavan Ln, Kadwa Sheri, Raopura, Vadodara</t>
   </si>
   <si>
-    <t>DOC1266</t>
-  </si>
-  <si>
     <t>Head and Neck Surgeon</t>
   </si>
   <si>
@@ -1173,9 +741,6 @@
     <t xml:space="preserve">Zydus hospital vadodara </t>
   </si>
   <si>
-    <t>DOC1267</t>
-  </si>
-  <si>
     <t>dharmendra vala</t>
   </si>
   <si>
@@ -1188,27 +753,18 @@
     <t xml:space="preserve">Samanvay hospital vadodara </t>
   </si>
   <si>
-    <t>DOC1285</t>
-  </si>
-  <si>
     <t>prutha patel</t>
   </si>
   <si>
     <t>9725704691</t>
   </si>
   <si>
-    <t>DOC1311</t>
-  </si>
-  <si>
     <t>ashish chavda</t>
   </si>
   <si>
     <t>8905902275</t>
   </si>
   <si>
-    <t>DOC1622</t>
-  </si>
-  <si>
     <t>nitant trivedi</t>
   </si>
   <si>
@@ -1218,9 +774,6 @@
     <t xml:space="preserve">Iris hospital anand </t>
   </si>
   <si>
-    <t>DOC1663</t>
-  </si>
-  <si>
     <t>anand</t>
   </si>
   <si>
@@ -1230,18 +783,12 @@
     <t>9967922652</t>
   </si>
   <si>
-    <t>DOC1664</t>
-  </si>
-  <si>
     <t>mit makadia</t>
   </si>
   <si>
     <t>7405558128</t>
   </si>
   <si>
-    <t>DOC1665</t>
-  </si>
-  <si>
     <t>khanjan shah</t>
   </si>
   <si>
@@ -1251,9 +798,6 @@
     <t xml:space="preserve">Zydus hospital anand </t>
   </si>
   <si>
-    <t>DOC1666</t>
-  </si>
-  <si>
     <t>jignesh rathod</t>
   </si>
   <si>
@@ -1266,9 +810,6 @@
     <t>Zydus hospital anand</t>
   </si>
   <si>
-    <t>DOC1667</t>
-  </si>
-  <si>
     <t>rajiv paliwal</t>
   </si>
   <si>
@@ -1278,27 +819,18 @@
     <t>9825056084</t>
   </si>
   <si>
-    <t>DOC1668</t>
-  </si>
-  <si>
     <t>jimmy patel</t>
   </si>
   <si>
     <t>9429085999</t>
   </si>
   <si>
-    <t>DOC1669</t>
-  </si>
-  <si>
     <t>darpan gandhi</t>
   </si>
   <si>
     <t>8200080044</t>
   </si>
   <si>
-    <t>DOC1670</t>
-  </si>
-  <si>
     <t>aayrin memon</t>
   </si>
   <si>
@@ -1314,9 +846,6 @@
     <t>Bhailal amin genral hospital vadodara</t>
   </si>
   <si>
-    <t>DOC1677</t>
-  </si>
-  <si>
     <t>rajat gusani</t>
   </si>
   <si>
@@ -1326,9 +855,6 @@
     <t>9313109865</t>
   </si>
   <si>
-    <t>DOC2095</t>
-  </si>
-  <si>
     <t>lalit nathani</t>
   </si>
   <si>
@@ -1344,9 +870,6 @@
     <t xml:space="preserve">Near pandya bridge vadodara </t>
   </si>
   <si>
-    <t>DOC2096</t>
-  </si>
-  <si>
     <t>himani ma'am</t>
   </si>
   <si>
@@ -1356,9 +879,6 @@
     <t xml:space="preserve">Banker super speciality hospital Manjalpur Vadodara </t>
   </si>
   <si>
-    <t>DOC2101</t>
-  </si>
-  <si>
     <t>mitesh sutariya</t>
   </si>
   <si>
@@ -1371,23 +891,308 @@
     <t>1st Vallabh Complex, Waghodia Rd, Near Parivar Char Rasta, Vadodara, Gujarat 390025</t>
   </si>
   <si>
-    <t>DOC2240</t>
-  </si>
-  <si>
-    <t>Report From : Doctors List</t>
-  </si>
-  <si>
-    <t>Date of File Download : Tue Aug 25 2026</t>
+    <t>DOC001</t>
+  </si>
+  <si>
+    <t>DOC002</t>
+  </si>
+  <si>
+    <t>DOC003</t>
+  </si>
+  <si>
+    <t>DOC004</t>
+  </si>
+  <si>
+    <t>DOC005</t>
+  </si>
+  <si>
+    <t>DOC006</t>
+  </si>
+  <si>
+    <t>DOC007</t>
+  </si>
+  <si>
+    <t>DOC008</t>
+  </si>
+  <si>
+    <t>DOC009</t>
+  </si>
+  <si>
+    <t>DOC010</t>
+  </si>
+  <si>
+    <t>DOC011</t>
+  </si>
+  <si>
+    <t>DOC012</t>
+  </si>
+  <si>
+    <t>DOC013</t>
+  </si>
+  <si>
+    <t>DOC014</t>
+  </si>
+  <si>
+    <t>DOC015</t>
+  </si>
+  <si>
+    <t>DOC016</t>
+  </si>
+  <si>
+    <t>DOC017</t>
+  </si>
+  <si>
+    <t>DOC018</t>
+  </si>
+  <si>
+    <t>DOC019</t>
+  </si>
+  <si>
+    <t>DOC020</t>
+  </si>
+  <si>
+    <t>DOC021</t>
+  </si>
+  <si>
+    <t>DOC022</t>
+  </si>
+  <si>
+    <t>DOC023</t>
+  </si>
+  <si>
+    <t>DOC024</t>
+  </si>
+  <si>
+    <t>DOC025</t>
+  </si>
+  <si>
+    <t>DOC026</t>
+  </si>
+  <si>
+    <t>DOC027</t>
+  </si>
+  <si>
+    <t>DOC028</t>
+  </si>
+  <si>
+    <t>DOC029</t>
+  </si>
+  <si>
+    <t>DOC030</t>
+  </si>
+  <si>
+    <t>DOC031</t>
+  </si>
+  <si>
+    <t>DOC032</t>
+  </si>
+  <si>
+    <t>DOC033</t>
+  </si>
+  <si>
+    <t>DOC034</t>
+  </si>
+  <si>
+    <t>DOC035</t>
+  </si>
+  <si>
+    <t>DOC036</t>
+  </si>
+  <si>
+    <t>DOC037</t>
+  </si>
+  <si>
+    <t>DOC038</t>
+  </si>
+  <si>
+    <t>DOC039</t>
+  </si>
+  <si>
+    <t>DOC040</t>
+  </si>
+  <si>
+    <t>DOC041</t>
+  </si>
+  <si>
+    <t>DOC042</t>
+  </si>
+  <si>
+    <t>DOC043</t>
+  </si>
+  <si>
+    <t>DOC044</t>
+  </si>
+  <si>
+    <t>DOC045</t>
+  </si>
+  <si>
+    <t>DOC046</t>
+  </si>
+  <si>
+    <t>DOC047</t>
+  </si>
+  <si>
+    <t>DOC048</t>
+  </si>
+  <si>
+    <t>DOC049</t>
+  </si>
+  <si>
+    <t>DOC050</t>
+  </si>
+  <si>
+    <t>DOC051</t>
+  </si>
+  <si>
+    <t>DOC052</t>
+  </si>
+  <si>
+    <t>DOC053</t>
+  </si>
+  <si>
+    <t>DOC054</t>
+  </si>
+  <si>
+    <t>DOC055</t>
+  </si>
+  <si>
+    <t>DOC056</t>
+  </si>
+  <si>
+    <t>DOC057</t>
+  </si>
+  <si>
+    <t>DOC058</t>
+  </si>
+  <si>
+    <t>DOC059</t>
+  </si>
+  <si>
+    <t>DOC060</t>
+  </si>
+  <si>
+    <t>DOC061</t>
+  </si>
+  <si>
+    <t>DOC062</t>
+  </si>
+  <si>
+    <t>DOC063</t>
+  </si>
+  <si>
+    <t>DOC064</t>
+  </si>
+  <si>
+    <t>DOC065</t>
+  </si>
+  <si>
+    <t>DOC066</t>
+  </si>
+  <si>
+    <t>DOC067</t>
+  </si>
+  <si>
+    <t>DOC068</t>
+  </si>
+  <si>
+    <t>DOC069</t>
+  </si>
+  <si>
+    <t>DOC070</t>
+  </si>
+  <si>
+    <t>DOC071</t>
+  </si>
+  <si>
+    <t>DOC072</t>
+  </si>
+  <si>
+    <t>DOC073</t>
+  </si>
+  <si>
+    <t>DOC074</t>
+  </si>
+  <si>
+    <t>DOC075</t>
+  </si>
+  <si>
+    <t>DOC076</t>
+  </si>
+  <si>
+    <t>DOC077</t>
+  </si>
+  <si>
+    <t>DOC078</t>
+  </si>
+  <si>
+    <t>DOC079</t>
+  </si>
+  <si>
+    <t>DOC080</t>
+  </si>
+  <si>
+    <t>DOC081</t>
+  </si>
+  <si>
+    <t>DOC082</t>
+  </si>
+  <si>
+    <t>DOC083</t>
+  </si>
+  <si>
+    <t>DOC084</t>
+  </si>
+  <si>
+    <t>DOC085</t>
+  </si>
+  <si>
+    <t>DOC086</t>
+  </si>
+  <si>
+    <t>DOC087</t>
+  </si>
+  <si>
+    <t>DOC088</t>
+  </si>
+  <si>
+    <t>DOC089</t>
+  </si>
+  <si>
+    <t>DOC090</t>
+  </si>
+  <si>
+    <t>DOC091</t>
+  </si>
+  <si>
+    <t>DOC092</t>
+  </si>
+  <si>
+    <t>DOC093</t>
+  </si>
+  <si>
+    <t>DOC094</t>
+  </si>
+  <si>
+    <t>DOC095</t>
+  </si>
+  <si>
+    <t>DOC096</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1754,17 +1559,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S97"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="113" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1823,7 +1629,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1855,45 +1661,42 @@
         <v>22</v>
       </c>
       <c r="K2" t="s">
+        <v>288</v>
+      </c>
+      <c r="L2" t="s">
         <v>23</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>24</v>
       </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" t="s">
         <v>26</v>
       </c>
-      <c r="O2" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
         <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
@@ -1914,16 +1717,13 @@
         <v>22</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>
@@ -1935,24 +1735,24 @@
         <v>22</v>
       </c>
       <c r="R3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
@@ -1973,16 +1773,13 @@
         <v>22</v>
       </c>
       <c r="K4" t="s">
-        <v>37</v>
+        <v>290</v>
       </c>
       <c r="L4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="O4" t="s">
         <v>22</v>
@@ -1994,24 +1791,24 @@
         <v>22</v>
       </c>
       <c r="R4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>22</v>
@@ -2032,16 +1829,13 @@
         <v>22</v>
       </c>
       <c r="K5" t="s">
-        <v>43</v>
+        <v>291</v>
       </c>
       <c r="L5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="O5" t="s">
         <v>22</v>
@@ -2053,24 +1847,24 @@
         <v>22</v>
       </c>
       <c r="R5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
         <v>22</v>
@@ -2085,22 +1879,19 @@
         <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="J6" t="s">
         <v>22</v>
       </c>
       <c r="K6" t="s">
-        <v>48</v>
+        <v>292</v>
       </c>
       <c r="L6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="M6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="O6" t="s">
         <v>22</v>
@@ -2112,24 +1903,24 @@
         <v>22</v>
       </c>
       <c r="R6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
@@ -2150,16 +1941,13 @@
         <v>22</v>
       </c>
       <c r="K7" t="s">
-        <v>53</v>
+        <v>293</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="O7" t="s">
         <v>22</v>
@@ -2171,24 +1959,24 @@
         <v>22</v>
       </c>
       <c r="R7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>22</v>
@@ -2209,16 +1997,13 @@
         <v>22</v>
       </c>
       <c r="K8" t="s">
-        <v>59</v>
+        <v>294</v>
       </c>
       <c r="L8" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="M8" t="s">
-        <v>61</v>
-      </c>
-      <c r="N8" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="O8" t="s">
         <v>22</v>
@@ -2230,24 +2015,24 @@
         <v>22</v>
       </c>
       <c r="R8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
@@ -2268,16 +2053,13 @@
         <v>22</v>
       </c>
       <c r="K9" t="s">
-        <v>66</v>
+        <v>295</v>
       </c>
       <c r="L9" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="M9" t="s">
-        <v>50</v>
-      </c>
-      <c r="N9" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="O9" t="s">
         <v>22</v>
@@ -2289,24 +2071,24 @@
         <v>22</v>
       </c>
       <c r="R9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
@@ -2327,16 +2109,13 @@
         <v>22</v>
       </c>
       <c r="K10" t="s">
-        <v>70</v>
+        <v>296</v>
       </c>
       <c r="L10" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="M10" t="s">
-        <v>61</v>
-      </c>
-      <c r="N10" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="O10" t="s">
         <v>22</v>
@@ -2348,24 +2127,24 @@
         <v>22</v>
       </c>
       <c r="R10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
@@ -2386,16 +2165,13 @@
         <v>22</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>297</v>
       </c>
       <c r="L11" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="M11" t="s">
-        <v>61</v>
-      </c>
-      <c r="N11" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="O11" t="s">
         <v>22</v>
@@ -2407,24 +2183,24 @@
         <v>22</v>
       </c>
       <c r="R11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
         <v>22</v>
@@ -2445,16 +2221,13 @@
         <v>22</v>
       </c>
       <c r="K12" t="s">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="L12" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="M12" t="s">
-        <v>61</v>
-      </c>
-      <c r="N12" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="O12" t="s">
         <v>22</v>
@@ -2466,24 +2239,24 @@
         <v>22</v>
       </c>
       <c r="R12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>22</v>
@@ -2504,16 +2277,13 @@
         <v>22</v>
       </c>
       <c r="K13" t="s">
-        <v>85</v>
+        <v>299</v>
       </c>
       <c r="L13" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="M13" t="s">
-        <v>25</v>
-      </c>
-      <c r="N13" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="O13" t="s">
         <v>22</v>
@@ -2525,24 +2295,24 @@
         <v>22</v>
       </c>
       <c r="R13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
         <v>22</v>
@@ -2563,16 +2333,13 @@
         <v>22</v>
       </c>
       <c r="K14" t="s">
-        <v>89</v>
+        <v>300</v>
       </c>
       <c r="L14" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="O14" t="s">
         <v>22</v>
@@ -2584,24 +2351,24 @@
         <v>22</v>
       </c>
       <c r="R14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
         <v>22</v>
@@ -2622,16 +2389,13 @@
         <v>22</v>
       </c>
       <c r="K15" t="s">
-        <v>93</v>
+        <v>301</v>
       </c>
       <c r="L15" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="M15" t="s">
-        <v>25</v>
-      </c>
-      <c r="N15" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="O15" t="s">
         <v>22</v>
@@ -2643,24 +2407,24 @@
         <v>22</v>
       </c>
       <c r="R15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
@@ -2681,16 +2445,13 @@
         <v>22</v>
       </c>
       <c r="K16" t="s">
-        <v>97</v>
+        <v>302</v>
       </c>
       <c r="L16" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="M16" t="s">
-        <v>61</v>
-      </c>
-      <c r="N16" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="O16" t="s">
         <v>22</v>
@@ -2702,24 +2463,24 @@
         <v>22</v>
       </c>
       <c r="R16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
@@ -2740,16 +2501,13 @@
         <v>22</v>
       </c>
       <c r="K17" t="s">
-        <v>39</v>
+        <v>303</v>
       </c>
       <c r="L17" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="M17" t="s">
-        <v>61</v>
-      </c>
-      <c r="N17" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="O17" t="s">
         <v>22</v>
@@ -2761,24 +2519,24 @@
         <v>22</v>
       </c>
       <c r="R17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
         <v>22</v>
@@ -2799,16 +2557,13 @@
         <v>22</v>
       </c>
       <c r="K18" t="s">
-        <v>104</v>
+        <v>304</v>
       </c>
       <c r="L18" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="M18" t="s">
-        <v>61</v>
-      </c>
-      <c r="N18" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="O18" t="s">
         <v>22</v>
@@ -2820,24 +2575,24 @@
         <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
         <v>22</v>
@@ -2858,16 +2613,13 @@
         <v>22</v>
       </c>
       <c r="K19" t="s">
-        <v>110</v>
+        <v>305</v>
       </c>
       <c r="L19" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="M19" t="s">
-        <v>50</v>
-      </c>
-      <c r="N19" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="O19" t="s">
         <v>22</v>
@@ -2879,24 +2631,24 @@
         <v>22</v>
       </c>
       <c r="R19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
         <v>22</v>
@@ -2917,16 +2669,13 @@
         <v>22</v>
       </c>
       <c r="K20" t="s">
-        <v>116</v>
+        <v>306</v>
       </c>
       <c r="L20" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="M20" t="s">
-        <v>50</v>
-      </c>
-      <c r="N20" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="O20" t="s">
         <v>22</v>
@@ -2938,18 +2687,18 @@
         <v>22</v>
       </c>
       <c r="R20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
         <v>20</v>
@@ -2976,16 +2725,13 @@
         <v>22</v>
       </c>
       <c r="K21" t="s">
-        <v>119</v>
+        <v>307</v>
       </c>
       <c r="L21" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="M21" t="s">
-        <v>25</v>
-      </c>
-      <c r="N21" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="O21" t="s">
         <v>22</v>
@@ -2997,24 +2743,24 @@
         <v>22</v>
       </c>
       <c r="R21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s">
         <v>22</v>
@@ -3035,16 +2781,13 @@
         <v>22</v>
       </c>
       <c r="K22" t="s">
-        <v>123</v>
+        <v>308</v>
       </c>
       <c r="L22" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="M22" t="s">
-        <v>25</v>
-      </c>
-      <c r="N22" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="O22" t="s">
         <v>22</v>
@@ -3056,24 +2799,24 @@
         <v>22</v>
       </c>
       <c r="R22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>22</v>
@@ -3094,16 +2837,13 @@
         <v>22</v>
       </c>
       <c r="K23" t="s">
-        <v>127</v>
+        <v>309</v>
       </c>
       <c r="L23" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>61</v>
-      </c>
-      <c r="N23" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="O23" t="s">
         <v>22</v>
@@ -3115,24 +2855,24 @@
         <v>22</v>
       </c>
       <c r="R23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s">
         <v>22</v>
@@ -3153,16 +2893,13 @@
         <v>22</v>
       </c>
       <c r="K24" t="s">
-        <v>131</v>
+        <v>310</v>
       </c>
       <c r="L24" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="M24" t="s">
-        <v>61</v>
-      </c>
-      <c r="N24" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="O24" t="s">
         <v>22</v>
@@ -3174,24 +2911,24 @@
         <v>22</v>
       </c>
       <c r="R24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S24" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E25" t="s">
         <v>22</v>
@@ -3212,16 +2949,13 @@
         <v>22</v>
       </c>
       <c r="K25" t="s">
-        <v>135</v>
+        <v>311</v>
       </c>
       <c r="L25" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="M25" t="s">
-        <v>50</v>
-      </c>
-      <c r="N25" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="O25" t="s">
         <v>22</v>
@@ -3233,24 +2967,24 @@
         <v>22</v>
       </c>
       <c r="R25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E26" t="s">
         <v>22</v>
@@ -3271,16 +3005,13 @@
         <v>22</v>
       </c>
       <c r="K26" t="s">
-        <v>139</v>
+        <v>312</v>
       </c>
       <c r="L26" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="M26" t="s">
-        <v>61</v>
-      </c>
-      <c r="N26" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="O26" t="s">
         <v>22</v>
@@ -3292,24 +3023,24 @@
         <v>22</v>
       </c>
       <c r="R26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s">
         <v>22</v>
@@ -3330,16 +3061,13 @@
         <v>22</v>
       </c>
       <c r="K27" t="s">
-        <v>144</v>
+        <v>313</v>
       </c>
       <c r="L27" t="s">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="M27" t="s">
-        <v>50</v>
-      </c>
-      <c r="N27" t="s">
-        <v>146</v>
+        <v>41</v>
       </c>
       <c r="O27" t="s">
         <v>22</v>
@@ -3351,24 +3079,24 @@
         <v>22</v>
       </c>
       <c r="R27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E28" t="s">
         <v>22</v>
@@ -3389,16 +3117,13 @@
         <v>22</v>
       </c>
       <c r="K28" t="s">
-        <v>148</v>
+        <v>314</v>
       </c>
       <c r="L28" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="M28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N28" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="O28" t="s">
         <v>22</v>
@@ -3410,24 +3135,24 @@
         <v>22</v>
       </c>
       <c r="R28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="E29" t="s">
         <v>22</v>
@@ -3448,16 +3173,13 @@
         <v>22</v>
       </c>
       <c r="K29" t="s">
-        <v>152</v>
+        <v>315</v>
       </c>
       <c r="L29" t="s">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="M29" t="s">
-        <v>25</v>
-      </c>
-      <c r="N29" t="s">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="O29" t="s">
         <v>22</v>
@@ -3469,24 +3191,24 @@
         <v>22</v>
       </c>
       <c r="R29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E30" t="s">
         <v>22</v>
@@ -3507,16 +3229,13 @@
         <v>22</v>
       </c>
       <c r="K30" t="s">
-        <v>156</v>
+        <v>316</v>
       </c>
       <c r="L30" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="M30" t="s">
-        <v>61</v>
-      </c>
-      <c r="N30" t="s">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="O30" t="s">
         <v>22</v>
@@ -3528,24 +3247,24 @@
         <v>22</v>
       </c>
       <c r="R30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E31" t="s">
         <v>22</v>
@@ -3566,16 +3285,13 @@
         <v>22</v>
       </c>
       <c r="K31" t="s">
-        <v>160</v>
+        <v>317</v>
       </c>
       <c r="L31" t="s">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="M31" t="s">
-        <v>61</v>
-      </c>
-      <c r="N31" t="s">
-        <v>162</v>
+        <v>48</v>
       </c>
       <c r="O31" t="s">
         <v>22</v>
@@ -3587,24 +3303,24 @@
         <v>22</v>
       </c>
       <c r="R31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E32" t="s">
         <v>22</v>
@@ -3625,16 +3341,13 @@
         <v>22</v>
       </c>
       <c r="K32" t="s">
-        <v>164</v>
+        <v>318</v>
       </c>
       <c r="L32" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="M32" t="s">
-        <v>50</v>
-      </c>
-      <c r="N32" t="s">
-        <v>166</v>
+        <v>41</v>
       </c>
       <c r="O32" t="s">
         <v>22</v>
@@ -3646,24 +3359,24 @@
         <v>22</v>
       </c>
       <c r="R32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="E33" t="s">
         <v>22</v>
@@ -3684,16 +3397,13 @@
         <v>22</v>
       </c>
       <c r="K33" t="s">
-        <v>170</v>
+        <v>319</v>
       </c>
       <c r="L33" t="s">
-        <v>171</v>
+        <v>109</v>
       </c>
       <c r="M33" t="s">
-        <v>50</v>
-      </c>
-      <c r="N33" t="s">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="O33" t="s">
         <v>22</v>
@@ -3705,24 +3415,24 @@
         <v>22</v>
       </c>
       <c r="R33" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E34" t="s">
         <v>22</v>
@@ -3743,16 +3453,13 @@
         <v>22</v>
       </c>
       <c r="K34" t="s">
-        <v>174</v>
+        <v>320</v>
       </c>
       <c r="L34" t="s">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="M34" t="s">
-        <v>61</v>
-      </c>
-      <c r="N34" t="s">
-        <v>176</v>
+        <v>48</v>
       </c>
       <c r="O34" t="s">
         <v>22</v>
@@ -3764,24 +3471,24 @@
         <v>22</v>
       </c>
       <c r="R34" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S34" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E35" t="s">
         <v>22</v>
@@ -3802,16 +3509,13 @@
         <v>22</v>
       </c>
       <c r="K35" t="s">
-        <v>178</v>
+        <v>321</v>
       </c>
       <c r="L35" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="M35" t="s">
-        <v>61</v>
-      </c>
-      <c r="N35" t="s">
-        <v>179</v>
+        <v>48</v>
       </c>
       <c r="O35" t="s">
         <v>22</v>
@@ -3823,24 +3527,24 @@
         <v>22</v>
       </c>
       <c r="R35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S35" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>180</v>
+        <v>113</v>
       </c>
       <c r="C36" t="s">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="D36" t="s">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="E36" t="s">
         <v>22</v>
@@ -3861,16 +3565,13 @@
         <v>22</v>
       </c>
       <c r="K36" t="s">
-        <v>183</v>
+        <v>322</v>
       </c>
       <c r="L36" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M36" t="s">
-        <v>61</v>
-      </c>
-      <c r="N36" t="s">
-        <v>184</v>
+        <v>48</v>
       </c>
       <c r="O36" t="s">
         <v>22</v>
@@ -3882,24 +3583,24 @@
         <v>22</v>
       </c>
       <c r="R36" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="D37" t="s">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="E37" t="s">
         <v>22</v>
@@ -3920,16 +3621,13 @@
         <v>22</v>
       </c>
       <c r="K37" t="s">
-        <v>186</v>
+        <v>323</v>
       </c>
       <c r="L37" t="s">
-        <v>187</v>
+        <v>117</v>
       </c>
       <c r="M37" t="s">
-        <v>25</v>
-      </c>
-      <c r="N37" t="s">
-        <v>188</v>
+        <v>24</v>
       </c>
       <c r="O37" t="s">
         <v>22</v>
@@ -3941,24 +3639,24 @@
         <v>22</v>
       </c>
       <c r="R37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S37" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E38" t="s">
         <v>22</v>
@@ -3979,16 +3677,13 @@
         <v>22</v>
       </c>
       <c r="K38" t="s">
-        <v>190</v>
+        <v>324</v>
       </c>
       <c r="L38" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="M38" t="s">
-        <v>25</v>
-      </c>
-      <c r="N38" t="s">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="O38" t="s">
         <v>22</v>
@@ -4000,24 +3695,24 @@
         <v>22</v>
       </c>
       <c r="R38" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E39" t="s">
         <v>22</v>
@@ -4038,16 +3733,13 @@
         <v>22</v>
       </c>
       <c r="K39" t="s">
-        <v>194</v>
+        <v>325</v>
       </c>
       <c r="L39" t="s">
-        <v>171</v>
+        <v>109</v>
       </c>
       <c r="M39" t="s">
-        <v>25</v>
-      </c>
-      <c r="N39" t="s">
-        <v>195</v>
+        <v>24</v>
       </c>
       <c r="O39" t="s">
         <v>22</v>
@@ -4059,24 +3751,24 @@
         <v>22</v>
       </c>
       <c r="R39" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S39" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>196</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D40" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E40" t="s">
         <v>22</v>
@@ -4097,16 +3789,13 @@
         <v>22</v>
       </c>
       <c r="K40" t="s">
-        <v>197</v>
+        <v>326</v>
       </c>
       <c r="L40" t="s">
-        <v>198</v>
+        <v>122</v>
       </c>
       <c r="M40" t="s">
-        <v>25</v>
-      </c>
-      <c r="N40" t="s">
-        <v>199</v>
+        <v>24</v>
       </c>
       <c r="O40" t="s">
         <v>22</v>
@@ -4118,24 +3807,24 @@
         <v>22</v>
       </c>
       <c r="R40" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S40" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>200</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E41" t="s">
         <v>22</v>
@@ -4156,16 +3845,13 @@
         <v>22</v>
       </c>
       <c r="K41" t="s">
-        <v>201</v>
+        <v>327</v>
       </c>
       <c r="L41" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="M41" t="s">
-        <v>50</v>
-      </c>
-      <c r="N41" t="s">
-        <v>202</v>
+        <v>41</v>
       </c>
       <c r="O41" t="s">
         <v>22</v>
@@ -4177,24 +3863,24 @@
         <v>22</v>
       </c>
       <c r="R41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S41" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>203</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E42" t="s">
         <v>22</v>
@@ -4215,16 +3901,13 @@
         <v>22</v>
       </c>
       <c r="K42" t="s">
-        <v>204</v>
+        <v>328</v>
       </c>
       <c r="L42" t="s">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="M42" t="s">
-        <v>50</v>
-      </c>
-      <c r="N42" t="s">
-        <v>206</v>
+        <v>41</v>
       </c>
       <c r="O42" t="s">
         <v>22</v>
@@ -4236,24 +3919,24 @@
         <v>22</v>
       </c>
       <c r="R42" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S42" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>207</v>
+        <v>126</v>
       </c>
       <c r="C43" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" t="s">
         <v>36</v>
-      </c>
-      <c r="D43" t="s">
-        <v>42</v>
       </c>
       <c r="E43" t="s">
         <v>22</v>
@@ -4274,16 +3957,13 @@
         <v>22</v>
       </c>
       <c r="K43" t="s">
-        <v>208</v>
+        <v>329</v>
       </c>
       <c r="L43" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="M43" t="s">
-        <v>25</v>
-      </c>
-      <c r="N43" t="s">
-        <v>210</v>
+        <v>24</v>
       </c>
       <c r="O43" t="s">
         <v>22</v>
@@ -4295,24 +3975,24 @@
         <v>22</v>
       </c>
       <c r="R43" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S43" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>211</v>
+        <v>128</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E44" t="s">
         <v>22</v>
@@ -4333,16 +4013,13 @@
         <v>22</v>
       </c>
       <c r="K44" t="s">
-        <v>212</v>
+        <v>330</v>
       </c>
       <c r="L44" t="s">
-        <v>213</v>
+        <v>129</v>
       </c>
       <c r="M44" t="s">
-        <v>50</v>
-      </c>
-      <c r="N44" t="s">
-        <v>214</v>
+        <v>41</v>
       </c>
       <c r="O44" t="s">
         <v>22</v>
@@ -4354,24 +4031,24 @@
         <v>22</v>
       </c>
       <c r="R44" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>215</v>
+        <v>130</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E45" t="s">
         <v>22</v>
@@ -4392,16 +4069,13 @@
         <v>22</v>
       </c>
       <c r="K45" t="s">
-        <v>216</v>
+        <v>331</v>
       </c>
       <c r="L45" t="s">
-        <v>217</v>
+        <v>131</v>
       </c>
       <c r="M45" t="s">
-        <v>25</v>
-      </c>
-      <c r="N45" t="s">
-        <v>218</v>
+        <v>24</v>
       </c>
       <c r="O45" t="s">
         <v>22</v>
@@ -4413,24 +4087,24 @@
         <v>22</v>
       </c>
       <c r="R45" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S45" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>219</v>
+        <v>132</v>
       </c>
       <c r="C46" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E46" t="s">
         <v>22</v>
@@ -4451,16 +4125,13 @@
         <v>22</v>
       </c>
       <c r="K46" t="s">
-        <v>220</v>
+        <v>332</v>
       </c>
       <c r="L46" t="s">
-        <v>221</v>
+        <v>133</v>
       </c>
       <c r="M46" t="s">
-        <v>61</v>
-      </c>
-      <c r="N46" t="s">
-        <v>222</v>
+        <v>48</v>
       </c>
       <c r="O46" t="s">
         <v>22</v>
@@ -4472,24 +4143,24 @@
         <v>22</v>
       </c>
       <c r="R46" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S46" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>223</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E47" t="s">
         <v>22</v>
@@ -4510,16 +4181,13 @@
         <v>22</v>
       </c>
       <c r="K47" t="s">
-        <v>224</v>
+        <v>333</v>
       </c>
       <c r="L47" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M47" t="s">
-        <v>25</v>
-      </c>
-      <c r="N47" t="s">
-        <v>225</v>
+        <v>24</v>
       </c>
       <c r="O47" t="s">
         <v>22</v>
@@ -4531,24 +4199,24 @@
         <v>22</v>
       </c>
       <c r="R47" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S47" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>226</v>
+        <v>135</v>
       </c>
       <c r="C48" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E48" t="s">
         <v>22</v>
@@ -4569,16 +4237,13 @@
         <v>22</v>
       </c>
       <c r="K48" t="s">
-        <v>227</v>
+        <v>334</v>
       </c>
       <c r="L48" t="s">
-        <v>228</v>
+        <v>136</v>
       </c>
       <c r="M48" t="s">
-        <v>50</v>
-      </c>
-      <c r="N48" t="s">
-        <v>229</v>
+        <v>41</v>
       </c>
       <c r="O48" t="s">
         <v>22</v>
@@ -4590,24 +4255,24 @@
         <v>22</v>
       </c>
       <c r="R48" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S48" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>230</v>
+        <v>137</v>
       </c>
       <c r="C49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" t="s">
         <v>36</v>
-      </c>
-      <c r="D49" t="s">
-        <v>42</v>
       </c>
       <c r="E49" t="s">
         <v>22</v>
@@ -4628,16 +4293,13 @@
         <v>22</v>
       </c>
       <c r="K49" t="s">
-        <v>231</v>
+        <v>335</v>
       </c>
       <c r="L49" t="s">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="M49" t="s">
-        <v>50</v>
-      </c>
-      <c r="N49" t="s">
-        <v>233</v>
+        <v>41</v>
       </c>
       <c r="O49" t="s">
         <v>22</v>
@@ -4649,24 +4311,24 @@
         <v>22</v>
       </c>
       <c r="R49" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S49" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>234</v>
+        <v>139</v>
       </c>
       <c r="C50" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>235</v>
+        <v>140</v>
       </c>
       <c r="E50" t="s">
         <v>22</v>
@@ -4687,16 +4349,13 @@
         <v>22</v>
       </c>
       <c r="K50" t="s">
-        <v>236</v>
+        <v>336</v>
       </c>
       <c r="L50" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="M50" t="s">
-        <v>25</v>
-      </c>
-      <c r="N50" t="s">
-        <v>238</v>
+        <v>24</v>
       </c>
       <c r="O50" t="s">
         <v>22</v>
@@ -4708,24 +4367,24 @@
         <v>22</v>
       </c>
       <c r="R50" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S50" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>239</v>
+        <v>142</v>
       </c>
       <c r="C51" t="s">
         <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>240</v>
+        <v>143</v>
       </c>
       <c r="E51" t="s">
         <v>22</v>
@@ -4746,16 +4405,13 @@
         <v>22</v>
       </c>
       <c r="K51" t="s">
-        <v>241</v>
+        <v>337</v>
       </c>
       <c r="L51" t="s">
-        <v>242</v>
+        <v>144</v>
       </c>
       <c r="M51" t="s">
-        <v>50</v>
-      </c>
-      <c r="N51" t="s">
-        <v>243</v>
+        <v>41</v>
       </c>
       <c r="O51" t="s">
         <v>22</v>
@@ -4767,24 +4423,24 @@
         <v>22</v>
       </c>
       <c r="R51" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S51" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>244</v>
+        <v>145</v>
       </c>
       <c r="C52" t="s">
-        <v>245</v>
+        <v>146</v>
       </c>
       <c r="D52" t="s">
-        <v>246</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
         <v>22</v>
@@ -4805,16 +4461,13 @@
         <v>22</v>
       </c>
       <c r="K52" t="s">
-        <v>247</v>
+        <v>338</v>
       </c>
       <c r="L52" t="s">
-        <v>248</v>
+        <v>148</v>
       </c>
       <c r="M52" t="s">
-        <v>25</v>
-      </c>
-      <c r="N52" t="s">
-        <v>249</v>
+        <v>24</v>
       </c>
       <c r="O52" t="s">
         <v>22</v>
@@ -4826,24 +4479,24 @@
         <v>22</v>
       </c>
       <c r="R52" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S52" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>250</v>
+        <v>149</v>
       </c>
       <c r="C53" t="s">
         <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>240</v>
+        <v>143</v>
       </c>
       <c r="E53" t="s">
         <v>22</v>
@@ -4864,16 +4517,13 @@
         <v>22</v>
       </c>
       <c r="K53" t="s">
-        <v>251</v>
+        <v>339</v>
       </c>
       <c r="L53" t="s">
-        <v>252</v>
+        <v>150</v>
       </c>
       <c r="M53" t="s">
-        <v>50</v>
-      </c>
-      <c r="N53" t="s">
-        <v>253</v>
+        <v>41</v>
       </c>
       <c r="O53" t="s">
         <v>22</v>
@@ -4885,24 +4535,24 @@
         <v>22</v>
       </c>
       <c r="R53" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S53" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="C54" t="s">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="D54" t="s">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="E54" t="s">
         <v>22</v>
@@ -4923,16 +4573,13 @@
         <v>22</v>
       </c>
       <c r="K54" t="s">
-        <v>256</v>
+        <v>340</v>
       </c>
       <c r="L54" t="s">
-        <v>257</v>
+        <v>153</v>
       </c>
       <c r="M54" t="s">
-        <v>50</v>
-      </c>
-      <c r="N54" t="s">
-        <v>258</v>
+        <v>41</v>
       </c>
       <c r="O54" t="s">
         <v>22</v>
@@ -4944,24 +4591,24 @@
         <v>22</v>
       </c>
       <c r="R54" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S54" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>259</v>
+        <v>154</v>
       </c>
       <c r="C55" t="s">
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>240</v>
+        <v>143</v>
       </c>
       <c r="E55" t="s">
         <v>22</v>
@@ -4982,16 +4629,13 @@
         <v>22</v>
       </c>
       <c r="K55" t="s">
-        <v>260</v>
+        <v>341</v>
       </c>
       <c r="L55" t="s">
-        <v>261</v>
+        <v>155</v>
       </c>
       <c r="M55" t="s">
-        <v>50</v>
-      </c>
-      <c r="N55" t="s">
-        <v>262</v>
+        <v>41</v>
       </c>
       <c r="O55" t="s">
         <v>22</v>
@@ -5003,24 +4647,24 @@
         <v>22</v>
       </c>
       <c r="R55" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S55" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>263</v>
+        <v>156</v>
       </c>
       <c r="C56" t="s">
-        <v>264</v>
+        <v>157</v>
       </c>
       <c r="D56" t="s">
-        <v>240</v>
+        <v>143</v>
       </c>
       <c r="E56" t="s">
         <v>22</v>
@@ -5041,16 +4685,13 @@
         <v>22</v>
       </c>
       <c r="K56" t="s">
-        <v>265</v>
+        <v>342</v>
       </c>
       <c r="L56" t="s">
-        <v>266</v>
+        <v>158</v>
       </c>
       <c r="M56" t="s">
-        <v>50</v>
-      </c>
-      <c r="N56" t="s">
-        <v>267</v>
+        <v>41</v>
       </c>
       <c r="O56" t="s">
         <v>22</v>
@@ -5062,18 +4703,18 @@
         <v>22</v>
       </c>
       <c r="R56" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S56" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>268</v>
+        <v>159</v>
       </c>
       <c r="C57" t="s">
         <v>20</v>
@@ -5100,16 +4741,13 @@
         <v>22</v>
       </c>
       <c r="K57" t="s">
-        <v>269</v>
+        <v>343</v>
       </c>
       <c r="L57" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="M57" t="s">
-        <v>25</v>
-      </c>
-      <c r="N57" t="s">
-        <v>270</v>
+        <v>24</v>
       </c>
       <c r="O57" t="s">
         <v>22</v>
@@ -5121,24 +4759,24 @@
         <v>22</v>
       </c>
       <c r="R57" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S57" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>271</v>
+        <v>160</v>
       </c>
       <c r="C58" t="s">
-        <v>272</v>
+        <v>161</v>
       </c>
       <c r="D58" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="E58" t="s">
         <v>22</v>
@@ -5159,16 +4797,13 @@
         <v>22</v>
       </c>
       <c r="K58" t="s">
-        <v>273</v>
+        <v>344</v>
       </c>
       <c r="L58" t="s">
-        <v>274</v>
+        <v>162</v>
       </c>
       <c r="M58" t="s">
-        <v>50</v>
-      </c>
-      <c r="N58" t="s">
-        <v>275</v>
+        <v>41</v>
       </c>
       <c r="O58" t="s">
         <v>22</v>
@@ -5180,24 +4815,24 @@
         <v>22</v>
       </c>
       <c r="R58" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S58" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>276</v>
+        <v>163</v>
       </c>
       <c r="C59" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D59" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E59" t="s">
         <v>22</v>
@@ -5218,16 +4853,13 @@
         <v>22</v>
       </c>
       <c r="K59" t="s">
-        <v>277</v>
+        <v>345</v>
       </c>
       <c r="L59" t="s">
-        <v>278</v>
+        <v>164</v>
       </c>
       <c r="M59" t="s">
-        <v>61</v>
-      </c>
-      <c r="N59" t="s">
-        <v>279</v>
+        <v>48</v>
       </c>
       <c r="O59" t="s">
         <v>22</v>
@@ -5239,24 +4871,24 @@
         <v>22</v>
       </c>
       <c r="R59" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S59" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>280</v>
+        <v>165</v>
       </c>
       <c r="C60" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D60" t="s">
-        <v>281</v>
+        <v>166</v>
       </c>
       <c r="E60" t="s">
         <v>22</v>
@@ -5277,16 +4909,13 @@
         <v>22</v>
       </c>
       <c r="K60" t="s">
-        <v>282</v>
+        <v>346</v>
       </c>
       <c r="L60" t="s">
-        <v>283</v>
+        <v>167</v>
       </c>
       <c r="M60" t="s">
-        <v>25</v>
-      </c>
-      <c r="N60" t="s">
-        <v>284</v>
+        <v>24</v>
       </c>
       <c r="O60" t="s">
         <v>22</v>
@@ -5298,24 +4927,24 @@
         <v>22</v>
       </c>
       <c r="R60" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S60" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>285</v>
+        <v>168</v>
       </c>
       <c r="C61" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D61" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E61" t="s">
         <v>22</v>
@@ -5336,16 +4965,13 @@
         <v>22</v>
       </c>
       <c r="K61" t="s">
-        <v>286</v>
+        <v>347</v>
       </c>
       <c r="L61" t="s">
-        <v>287</v>
+        <v>169</v>
       </c>
       <c r="M61" t="s">
-        <v>25</v>
-      </c>
-      <c r="N61" t="s">
-        <v>288</v>
+        <v>24</v>
       </c>
       <c r="O61" t="s">
         <v>22</v>
@@ -5357,24 +4983,24 @@
         <v>22</v>
       </c>
       <c r="R61" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S61" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>289</v>
+        <v>170</v>
       </c>
       <c r="C62" t="s">
-        <v>290</v>
+        <v>171</v>
       </c>
       <c r="D62" t="s">
-        <v>291</v>
+        <v>172</v>
       </c>
       <c r="E62" t="s">
         <v>22</v>
@@ -5395,16 +5021,13 @@
         <v>22</v>
       </c>
       <c r="K62" t="s">
-        <v>292</v>
+        <v>348</v>
       </c>
       <c r="L62" t="s">
-        <v>293</v>
+        <v>173</v>
       </c>
       <c r="M62" t="s">
-        <v>61</v>
-      </c>
-      <c r="N62" t="s">
-        <v>294</v>
+        <v>48</v>
       </c>
       <c r="O62" t="s">
         <v>22</v>
@@ -5416,24 +5039,24 @@
         <v>22</v>
       </c>
       <c r="R62" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S62" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>295</v>
+        <v>174</v>
       </c>
       <c r="C63" t="s">
-        <v>290</v>
+        <v>171</v>
       </c>
       <c r="D63" t="s">
-        <v>291</v>
+        <v>172</v>
       </c>
       <c r="E63" t="s">
         <v>22</v>
@@ -5454,16 +5077,13 @@
         <v>22</v>
       </c>
       <c r="K63" t="s">
-        <v>296</v>
+        <v>349</v>
       </c>
       <c r="L63" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M63" t="s">
-        <v>50</v>
-      </c>
-      <c r="N63" t="s">
-        <v>297</v>
+        <v>41</v>
       </c>
       <c r="O63" t="s">
         <v>22</v>
@@ -5475,24 +5095,24 @@
         <v>22</v>
       </c>
       <c r="R63" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S63" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>298</v>
+        <v>175</v>
       </c>
       <c r="C64" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D64" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E64" t="s">
         <v>22</v>
@@ -5513,16 +5133,13 @@
         <v>22</v>
       </c>
       <c r="K64" t="s">
-        <v>299</v>
+        <v>350</v>
       </c>
       <c r="L64" t="s">
-        <v>300</v>
+        <v>176</v>
       </c>
       <c r="M64" t="s">
-        <v>50</v>
-      </c>
-      <c r="N64" t="s">
-        <v>301</v>
+        <v>41</v>
       </c>
       <c r="O64" t="s">
         <v>22</v>
@@ -5534,24 +5151,24 @@
         <v>22</v>
       </c>
       <c r="R64" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S64" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>302</v>
+        <v>177</v>
       </c>
       <c r="C65" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D65" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E65" t="s">
         <v>22</v>
@@ -5572,16 +5189,13 @@
         <v>22</v>
       </c>
       <c r="K65" t="s">
-        <v>303</v>
+        <v>351</v>
       </c>
       <c r="L65" t="s">
-        <v>304</v>
+        <v>178</v>
       </c>
       <c r="M65" t="s">
-        <v>50</v>
-      </c>
-      <c r="N65" t="s">
-        <v>305</v>
+        <v>41</v>
       </c>
       <c r="O65" t="s">
         <v>22</v>
@@ -5593,24 +5207,24 @@
         <v>22</v>
       </c>
       <c r="R65" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S65" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>306</v>
+        <v>179</v>
       </c>
       <c r="C66" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D66" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E66" t="s">
         <v>22</v>
@@ -5631,16 +5245,13 @@
         <v>22</v>
       </c>
       <c r="K66" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="L66" t="s">
-        <v>308</v>
+        <v>180</v>
       </c>
       <c r="M66" t="s">
-        <v>61</v>
-      </c>
-      <c r="N66" t="s">
-        <v>309</v>
+        <v>48</v>
       </c>
       <c r="O66" t="s">
         <v>22</v>
@@ -5652,24 +5263,24 @@
         <v>22</v>
       </c>
       <c r="R66" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S66" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>310</v>
+        <v>181</v>
       </c>
       <c r="C67" t="s">
-        <v>311</v>
+        <v>182</v>
       </c>
       <c r="D67" t="s">
-        <v>240</v>
+        <v>143</v>
       </c>
       <c r="E67" t="s">
         <v>22</v>
@@ -5684,25 +5295,22 @@
         <v>22</v>
       </c>
       <c r="I67" t="s">
-        <v>312</v>
+        <v>183</v>
       </c>
       <c r="J67" t="s">
         <v>22</v>
       </c>
       <c r="K67" t="s">
-        <v>313</v>
+        <v>353</v>
       </c>
       <c r="L67" t="s">
-        <v>314</v>
+        <v>184</v>
       </c>
       <c r="M67" t="s">
-        <v>50</v>
-      </c>
-      <c r="N67" t="s">
-        <v>315</v>
+        <v>41</v>
       </c>
       <c r="O67" t="s">
-        <v>316</v>
+        <v>185</v>
       </c>
       <c r="P67" t="s">
         <v>22</v>
@@ -5711,24 +5319,24 @@
         <v>22</v>
       </c>
       <c r="R67" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S67" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>317</v>
+        <v>186</v>
       </c>
       <c r="C68" t="s">
-        <v>245</v>
+        <v>146</v>
       </c>
       <c r="D68" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="E68" t="s">
         <v>22</v>
@@ -5743,22 +5351,19 @@
         <v>22</v>
       </c>
       <c r="I68" t="s">
-        <v>318</v>
+        <v>187</v>
       </c>
       <c r="J68" t="s">
         <v>22</v>
       </c>
       <c r="K68" t="s">
-        <v>22</v>
+        <v>354</v>
       </c>
       <c r="L68" t="s">
-        <v>319</v>
+        <v>188</v>
       </c>
       <c r="M68" t="s">
-        <v>50</v>
-      </c>
-      <c r="N68" t="s">
-        <v>320</v>
+        <v>41</v>
       </c>
       <c r="O68" t="s">
         <v>22</v>
@@ -5770,24 +5375,24 @@
         <v>22</v>
       </c>
       <c r="R68" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S68" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>321</v>
+        <v>189</v>
       </c>
       <c r="C69" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D69" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E69" t="s">
         <v>22</v>
@@ -5802,22 +5407,19 @@
         <v>22</v>
       </c>
       <c r="I69" t="s">
-        <v>322</v>
+        <v>190</v>
       </c>
       <c r="J69" t="s">
         <v>22</v>
       </c>
       <c r="K69" t="s">
-        <v>22</v>
+        <v>355</v>
       </c>
       <c r="L69" t="s">
-        <v>323</v>
+        <v>191</v>
       </c>
       <c r="M69" t="s">
-        <v>61</v>
-      </c>
-      <c r="N69" t="s">
-        <v>324</v>
+        <v>48</v>
       </c>
       <c r="O69" t="s">
         <v>22</v>
@@ -5829,24 +5431,24 @@
         <v>22</v>
       </c>
       <c r="R69" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S69" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>325</v>
+        <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D70" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="E70" t="s">
         <v>22</v>
@@ -5861,22 +5463,19 @@
         <v>22</v>
       </c>
       <c r="I70" t="s">
-        <v>326</v>
+        <v>193</v>
       </c>
       <c r="J70" t="s">
         <v>22</v>
       </c>
       <c r="K70" t="s">
-        <v>22</v>
+        <v>356</v>
       </c>
       <c r="L70" t="s">
-        <v>327</v>
+        <v>194</v>
       </c>
       <c r="M70" t="s">
-        <v>50</v>
-      </c>
-      <c r="N70" t="s">
-        <v>328</v>
+        <v>41</v>
       </c>
       <c r="O70" t="s">
         <v>22</v>
@@ -5888,24 +5487,24 @@
         <v>22</v>
       </c>
       <c r="R70" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S70" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>329</v>
+        <v>195</v>
       </c>
       <c r="C71" t="s">
         <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>196</v>
       </c>
       <c r="E71" t="s">
         <v>22</v>
@@ -5920,22 +5519,19 @@
         <v>22</v>
       </c>
       <c r="I71" t="s">
-        <v>331</v>
+        <v>197</v>
       </c>
       <c r="J71" t="s">
         <v>22</v>
       </c>
       <c r="K71" t="s">
-        <v>22</v>
+        <v>357</v>
       </c>
       <c r="L71" t="s">
-        <v>332</v>
+        <v>198</v>
       </c>
       <c r="M71" t="s">
-        <v>50</v>
-      </c>
-      <c r="N71" t="s">
-        <v>333</v>
+        <v>41</v>
       </c>
       <c r="O71" t="s">
         <v>22</v>
@@ -5947,24 +5543,24 @@
         <v>22</v>
       </c>
       <c r="R71" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S71" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>334</v>
+        <v>199</v>
       </c>
       <c r="C72" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>200</v>
       </c>
       <c r="E72" t="s">
         <v>22</v>
@@ -5979,22 +5575,19 @@
         <v>22</v>
       </c>
       <c r="I72" t="s">
-        <v>336</v>
+        <v>201</v>
       </c>
       <c r="J72" t="s">
         <v>22</v>
       </c>
       <c r="K72" t="s">
-        <v>22</v>
+        <v>358</v>
       </c>
       <c r="L72" t="s">
-        <v>257</v>
+        <v>153</v>
       </c>
       <c r="M72" t="s">
-        <v>25</v>
-      </c>
-      <c r="N72" t="s">
-        <v>337</v>
+        <v>24</v>
       </c>
       <c r="O72" t="s">
         <v>22</v>
@@ -6006,25 +5599,25 @@
         <v>22</v>
       </c>
       <c r="R72" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S72" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>338</v>
+        <v>202</v>
       </c>
       <c r="C73" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73" t="s">
         <v>36</v>
       </c>
-      <c r="D73" t="s">
-        <v>42</v>
-      </c>
       <c r="E73" t="s">
         <v>22</v>
       </c>
@@ -6038,22 +5631,19 @@
         <v>22</v>
       </c>
       <c r="I73" t="s">
-        <v>339</v>
+        <v>203</v>
       </c>
       <c r="J73" t="s">
         <v>22</v>
       </c>
       <c r="K73" t="s">
-        <v>22</v>
+        <v>359</v>
       </c>
       <c r="L73" t="s">
-        <v>340</v>
+        <v>204</v>
       </c>
       <c r="M73" t="s">
-        <v>25</v>
-      </c>
-      <c r="N73" t="s">
-        <v>341</v>
+        <v>24</v>
       </c>
       <c r="O73" t="s">
         <v>22</v>
@@ -6065,27 +5655,27 @@
         <v>22</v>
       </c>
       <c r="R73" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S73" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>342</v>
+        <v>205</v>
       </c>
       <c r="C74" t="s">
+        <v>32</v>
+      </c>
+      <c r="D74" t="s">
         <v>36</v>
       </c>
-      <c r="D74" t="s">
-        <v>42</v>
-      </c>
       <c r="E74" t="s">
-        <v>343</v>
+        <v>206</v>
       </c>
       <c r="F74" t="s">
         <v>22</v>
@@ -6097,22 +5687,19 @@
         <v>22</v>
       </c>
       <c r="I74" t="s">
-        <v>344</v>
+        <v>207</v>
       </c>
       <c r="J74" t="s">
         <v>22</v>
       </c>
       <c r="K74" t="s">
-        <v>22</v>
+        <v>360</v>
       </c>
       <c r="L74" t="s">
         <v>22</v>
       </c>
       <c r="M74" t="s">
-        <v>61</v>
-      </c>
-      <c r="N74" t="s">
-        <v>345</v>
+        <v>48</v>
       </c>
       <c r="O74" t="s">
         <v>22</v>
@@ -6124,24 +5711,24 @@
         <v>22</v>
       </c>
       <c r="R74" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S74" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>346</v>
+        <v>208</v>
       </c>
       <c r="C75" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D75" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E75" t="s">
         <v>22</v>
@@ -6156,22 +5743,19 @@
         <v>22</v>
       </c>
       <c r="I75" t="s">
-        <v>347</v>
+        <v>209</v>
       </c>
       <c r="J75" t="s">
         <v>22</v>
       </c>
       <c r="K75" t="s">
-        <v>22</v>
+        <v>361</v>
       </c>
       <c r="L75" t="s">
-        <v>348</v>
+        <v>210</v>
       </c>
       <c r="M75" t="s">
-        <v>61</v>
-      </c>
-      <c r="N75" t="s">
-        <v>349</v>
+        <v>48</v>
       </c>
       <c r="O75" t="s">
         <v>22</v>
@@ -6183,24 +5767,24 @@
         <v>22</v>
       </c>
       <c r="R75" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S75" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>350</v>
+        <v>211</v>
       </c>
       <c r="C76" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D76" t="s">
-        <v>351</v>
+        <v>212</v>
       </c>
       <c r="E76" t="s">
         <v>22</v>
@@ -6215,22 +5799,19 @@
         <v>22</v>
       </c>
       <c r="I76" t="s">
-        <v>352</v>
+        <v>213</v>
       </c>
       <c r="J76" t="s">
         <v>22</v>
       </c>
       <c r="K76" t="s">
-        <v>22</v>
+        <v>362</v>
       </c>
       <c r="L76" t="s">
         <v>22</v>
       </c>
       <c r="M76" t="s">
-        <v>61</v>
-      </c>
-      <c r="N76" t="s">
-        <v>353</v>
+        <v>48</v>
       </c>
       <c r="O76" t="s">
         <v>22</v>
@@ -6239,27 +5820,27 @@
         <v>22</v>
       </c>
       <c r="Q76" t="s">
-        <v>354</v>
+        <v>214</v>
       </c>
       <c r="R76" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S76" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>355</v>
+        <v>215</v>
       </c>
       <c r="C77" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D77" t="s">
-        <v>356</v>
+        <v>216</v>
       </c>
       <c r="E77" t="s">
         <v>22</v>
@@ -6274,22 +5855,19 @@
         <v>22</v>
       </c>
       <c r="I77" t="s">
-        <v>357</v>
+        <v>217</v>
       </c>
       <c r="J77" t="s">
         <v>22</v>
       </c>
       <c r="K77" t="s">
-        <v>22</v>
+        <v>363</v>
       </c>
       <c r="L77" t="s">
-        <v>358</v>
+        <v>218</v>
       </c>
       <c r="M77" t="s">
-        <v>61</v>
-      </c>
-      <c r="N77" t="s">
-        <v>359</v>
+        <v>48</v>
       </c>
       <c r="O77" t="s">
         <v>22</v>
@@ -6298,30 +5876,30 @@
         <v>22</v>
       </c>
       <c r="Q77" t="s">
-        <v>360</v>
+        <v>219</v>
       </c>
       <c r="R77" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S77" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>361</v>
+        <v>220</v>
       </c>
       <c r="C78" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D78" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>362</v>
+        <v>221</v>
       </c>
       <c r="F78" t="s">
         <v>22</v>
@@ -6333,22 +5911,19 @@
         <v>22</v>
       </c>
       <c r="I78" t="s">
-        <v>363</v>
+        <v>222</v>
       </c>
       <c r="J78" t="s">
         <v>22</v>
       </c>
       <c r="K78" t="s">
-        <v>22</v>
+        <v>364</v>
       </c>
       <c r="L78" t="s">
-        <v>364</v>
+        <v>223</v>
       </c>
       <c r="M78" t="s">
-        <v>61</v>
-      </c>
-      <c r="N78" t="s">
-        <v>365</v>
+        <v>48</v>
       </c>
       <c r="O78" t="s">
         <v>22</v>
@@ -6360,27 +5935,27 @@
         <v>22</v>
       </c>
       <c r="R78" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S78" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>366</v>
+        <v>224</v>
       </c>
       <c r="C79" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D79" t="s">
-        <v>330</v>
+        <v>196</v>
       </c>
       <c r="E79" t="s">
-        <v>367</v>
+        <v>225</v>
       </c>
       <c r="F79" t="s">
         <v>22</v>
@@ -6392,22 +5967,19 @@
         <v>22</v>
       </c>
       <c r="I79" t="s">
-        <v>368</v>
+        <v>226</v>
       </c>
       <c r="J79" t="s">
         <v>22</v>
       </c>
       <c r="K79" t="s">
-        <v>22</v>
+        <v>365</v>
       </c>
       <c r="L79" t="s">
-        <v>369</v>
+        <v>227</v>
       </c>
       <c r="M79" t="s">
-        <v>50</v>
-      </c>
-      <c r="N79" t="s">
-        <v>370</v>
+        <v>41</v>
       </c>
       <c r="O79" t="s">
         <v>22</v>
@@ -6416,27 +5988,27 @@
         <v>22</v>
       </c>
       <c r="Q79" t="s">
-        <v>371</v>
+        <v>228</v>
       </c>
       <c r="R79" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S79" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>372</v>
+        <v>229</v>
       </c>
       <c r="C80" t="s">
-        <v>373</v>
+        <v>230</v>
       </c>
       <c r="D80" t="s">
-        <v>351</v>
+        <v>212</v>
       </c>
       <c r="E80" t="s">
         <v>22</v>
@@ -6451,22 +6023,19 @@
         <v>22</v>
       </c>
       <c r="I80" t="s">
-        <v>374</v>
+        <v>231</v>
       </c>
       <c r="J80" t="s">
         <v>22</v>
       </c>
       <c r="K80" t="s">
-        <v>22</v>
+        <v>366</v>
       </c>
       <c r="L80" t="s">
-        <v>375</v>
+        <v>232</v>
       </c>
       <c r="M80" t="s">
-        <v>61</v>
-      </c>
-      <c r="N80" t="s">
-        <v>376</v>
+        <v>48</v>
       </c>
       <c r="O80" t="s">
         <v>22</v>
@@ -6475,30 +6044,30 @@
         <v>22</v>
       </c>
       <c r="Q80" t="s">
-        <v>377</v>
+        <v>233</v>
       </c>
       <c r="R80" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S80" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>378</v>
+        <v>234</v>
       </c>
       <c r="C81" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D81" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E81" t="s">
-        <v>379</v>
+        <v>235</v>
       </c>
       <c r="F81" t="s">
         <v>22</v>
@@ -6510,22 +6079,19 @@
         <v>22</v>
       </c>
       <c r="I81" t="s">
-        <v>380</v>
+        <v>236</v>
       </c>
       <c r="J81" t="s">
         <v>22</v>
       </c>
       <c r="K81" t="s">
-        <v>22</v>
+        <v>367</v>
       </c>
       <c r="L81" t="s">
-        <v>381</v>
+        <v>237</v>
       </c>
       <c r="M81" t="s">
-        <v>61</v>
-      </c>
-      <c r="N81" t="s">
-        <v>382</v>
+        <v>48</v>
       </c>
       <c r="O81" t="s">
         <v>22</v>
@@ -6537,27 +6103,27 @@
         <v>22</v>
       </c>
       <c r="R81" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S81" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>383</v>
+        <v>238</v>
       </c>
       <c r="C82" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" t="s">
         <v>36</v>
       </c>
-      <c r="D82" t="s">
-        <v>42</v>
-      </c>
       <c r="E82" t="s">
-        <v>384</v>
+        <v>239</v>
       </c>
       <c r="F82" t="s">
         <v>22</v>
@@ -6569,22 +6135,19 @@
         <v>22</v>
       </c>
       <c r="I82" t="s">
-        <v>385</v>
+        <v>240</v>
       </c>
       <c r="J82" t="s">
         <v>22</v>
       </c>
       <c r="K82" t="s">
-        <v>22</v>
+        <v>368</v>
       </c>
       <c r="L82" t="s">
-        <v>386</v>
+        <v>241</v>
       </c>
       <c r="M82" t="s">
-        <v>61</v>
-      </c>
-      <c r="N82" t="s">
-        <v>387</v>
+        <v>48</v>
       </c>
       <c r="O82" t="s">
         <v>22</v>
@@ -6596,27 +6159,27 @@
         <v>22</v>
       </c>
       <c r="R82" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S82" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>388</v>
+        <v>242</v>
       </c>
       <c r="C83" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D83" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="E83" t="s">
-        <v>379</v>
+        <v>235</v>
       </c>
       <c r="F83" t="s">
         <v>22</v>
@@ -6628,22 +6191,19 @@
         <v>22</v>
       </c>
       <c r="I83" t="s">
-        <v>389</v>
+        <v>243</v>
       </c>
       <c r="J83" t="s">
         <v>22</v>
       </c>
       <c r="K83" t="s">
-        <v>22</v>
+        <v>369</v>
       </c>
       <c r="L83" t="s">
         <v>22</v>
       </c>
       <c r="M83" t="s">
-        <v>61</v>
-      </c>
-      <c r="N83" t="s">
-        <v>390</v>
+        <v>48</v>
       </c>
       <c r="O83" t="s">
         <v>22</v>
@@ -6655,25 +6215,25 @@
         <v>22</v>
       </c>
       <c r="R83" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S83" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="84" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>391</v>
+        <v>244</v>
       </c>
       <c r="C84" t="s">
+        <v>32</v>
+      </c>
+      <c r="D84" t="s">
         <v>36</v>
       </c>
-      <c r="D84" t="s">
-        <v>42</v>
-      </c>
       <c r="E84" t="s">
         <v>22</v>
       </c>
@@ -6687,22 +6247,19 @@
         <v>22</v>
       </c>
       <c r="I84" t="s">
-        <v>392</v>
+        <v>245</v>
       </c>
       <c r="J84" t="s">
         <v>22</v>
       </c>
       <c r="K84" t="s">
-        <v>22</v>
+        <v>370</v>
       </c>
       <c r="L84" t="s">
-        <v>348</v>
+        <v>210</v>
       </c>
       <c r="M84" t="s">
-        <v>50</v>
-      </c>
-      <c r="N84" t="s">
-        <v>393</v>
+        <v>41</v>
       </c>
       <c r="O84" t="s">
         <v>22</v>
@@ -6714,25 +6271,25 @@
         <v>22</v>
       </c>
       <c r="R84" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S84" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>394</v>
+        <v>246</v>
       </c>
       <c r="C85" t="s">
+        <v>32</v>
+      </c>
+      <c r="D85" t="s">
         <v>36</v>
       </c>
-      <c r="D85" t="s">
-        <v>42</v>
-      </c>
       <c r="E85" t="s">
         <v>22</v>
       </c>
@@ -6746,22 +6303,19 @@
         <v>22</v>
       </c>
       <c r="I85" t="s">
-        <v>395</v>
+        <v>247</v>
       </c>
       <c r="J85" t="s">
         <v>22</v>
       </c>
       <c r="K85" t="s">
-        <v>22</v>
+        <v>371</v>
       </c>
       <c r="L85" t="s">
-        <v>396</v>
+        <v>248</v>
       </c>
       <c r="M85" t="s">
-        <v>50</v>
-      </c>
-      <c r="N85" t="s">
-        <v>397</v>
+        <v>41</v>
       </c>
       <c r="O85" t="s">
         <v>22</v>
@@ -6773,24 +6327,24 @@
         <v>22</v>
       </c>
       <c r="R85" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S85" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="86" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>399</v>
+        <v>250</v>
       </c>
       <c r="C86" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D86" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E86" t="s">
         <v>22</v>
@@ -6805,22 +6359,19 @@
         <v>22</v>
       </c>
       <c r="I86" t="s">
-        <v>400</v>
+        <v>251</v>
       </c>
       <c r="J86" t="s">
         <v>22</v>
       </c>
       <c r="K86" t="s">
-        <v>22</v>
+        <v>372</v>
       </c>
       <c r="L86" t="s">
-        <v>396</v>
+        <v>248</v>
       </c>
       <c r="M86" t="s">
-        <v>50</v>
-      </c>
-      <c r="N86" t="s">
-        <v>401</v>
+        <v>41</v>
       </c>
       <c r="O86" t="s">
         <v>22</v>
@@ -6832,24 +6383,24 @@
         <v>22</v>
       </c>
       <c r="R86" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S86" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>402</v>
+        <v>252</v>
       </c>
       <c r="C87" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D87" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E87" t="s">
         <v>22</v>
@@ -6864,22 +6415,19 @@
         <v>22</v>
       </c>
       <c r="I87" t="s">
-        <v>403</v>
+        <v>253</v>
       </c>
       <c r="J87" t="s">
         <v>22</v>
       </c>
       <c r="K87" t="s">
-        <v>22</v>
+        <v>373</v>
       </c>
       <c r="L87" t="s">
-        <v>396</v>
+        <v>248</v>
       </c>
       <c r="M87" t="s">
-        <v>50</v>
-      </c>
-      <c r="N87" t="s">
-        <v>404</v>
+        <v>41</v>
       </c>
       <c r="O87" t="s">
         <v>22</v>
@@ -6891,25 +6439,25 @@
         <v>22</v>
       </c>
       <c r="R87" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S87" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="88" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>405</v>
+        <v>254</v>
       </c>
       <c r="C88" t="s">
+        <v>32</v>
+      </c>
+      <c r="D88" t="s">
         <v>36</v>
       </c>
-      <c r="D88" t="s">
-        <v>42</v>
-      </c>
       <c r="E88" t="s">
         <v>22</v>
       </c>
@@ -6923,22 +6471,19 @@
         <v>22</v>
       </c>
       <c r="I88" t="s">
-        <v>406</v>
+        <v>255</v>
       </c>
       <c r="J88" t="s">
         <v>22</v>
       </c>
       <c r="K88" t="s">
-        <v>22</v>
+        <v>374</v>
       </c>
       <c r="L88" t="s">
-        <v>407</v>
+        <v>256</v>
       </c>
       <c r="M88" t="s">
-        <v>50</v>
-      </c>
-      <c r="N88" t="s">
-        <v>408</v>
+        <v>41</v>
       </c>
       <c r="O88" t="s">
         <v>22</v>
@@ -6950,24 +6495,24 @@
         <v>22</v>
       </c>
       <c r="R88" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S88" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>409</v>
+        <v>257</v>
       </c>
       <c r="C89" t="s">
         <v>20</v>
       </c>
       <c r="D89" t="s">
-        <v>330</v>
+        <v>196</v>
       </c>
       <c r="E89" t="s">
         <v>22</v>
@@ -6979,25 +6524,22 @@
         <v>22</v>
       </c>
       <c r="H89" t="s">
-        <v>410</v>
+        <v>258</v>
       </c>
       <c r="I89" t="s">
-        <v>411</v>
+        <v>259</v>
       </c>
       <c r="J89" t="s">
         <v>22</v>
       </c>
       <c r="K89" t="s">
-        <v>22</v>
+        <v>375</v>
       </c>
       <c r="L89" t="s">
-        <v>412</v>
+        <v>260</v>
       </c>
       <c r="M89" t="s">
-        <v>50</v>
-      </c>
-      <c r="N89" t="s">
-        <v>413</v>
+        <v>41</v>
       </c>
       <c r="O89" t="s">
         <v>22</v>
@@ -7009,24 +6551,24 @@
         <v>22</v>
       </c>
       <c r="R89" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S89" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>414</v>
+        <v>261</v>
       </c>
       <c r="C90" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D90" t="s">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="E90" t="s">
         <v>22</v>
@@ -7038,25 +6580,22 @@
         <v>22</v>
       </c>
       <c r="H90" t="s">
-        <v>415</v>
+        <v>262</v>
       </c>
       <c r="I90" t="s">
-        <v>416</v>
+        <v>263</v>
       </c>
       <c r="J90" t="s">
         <v>22</v>
       </c>
       <c r="K90" t="s">
-        <v>22</v>
+        <v>376</v>
       </c>
       <c r="L90" t="s">
-        <v>412</v>
+        <v>260</v>
       </c>
       <c r="M90" t="s">
-        <v>50</v>
-      </c>
-      <c r="N90" t="s">
-        <v>417</v>
+        <v>41</v>
       </c>
       <c r="O90" t="s">
         <v>22</v>
@@ -7068,24 +6607,24 @@
         <v>22</v>
       </c>
       <c r="R90" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S90" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>418</v>
+        <v>264</v>
       </c>
       <c r="C91" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D91" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E91" t="s">
         <v>22</v>
@@ -7100,22 +6639,19 @@
         <v>22</v>
       </c>
       <c r="I91" t="s">
-        <v>419</v>
+        <v>265</v>
       </c>
       <c r="J91" t="s">
         <v>22</v>
       </c>
       <c r="K91" t="s">
-        <v>22</v>
+        <v>377</v>
       </c>
       <c r="L91" t="s">
-        <v>407</v>
+        <v>256</v>
       </c>
       <c r="M91" t="s">
-        <v>50</v>
-      </c>
-      <c r="N91" t="s">
-        <v>420</v>
+        <v>41</v>
       </c>
       <c r="O91" t="s">
         <v>22</v>
@@ -7127,24 +6663,24 @@
         <v>22</v>
       </c>
       <c r="R91" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S91" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>421</v>
+        <v>266</v>
       </c>
       <c r="C92" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D92" t="s">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="E92" t="s">
         <v>22</v>
@@ -7159,22 +6695,19 @@
         <v>22</v>
       </c>
       <c r="I92" t="s">
-        <v>422</v>
+        <v>267</v>
       </c>
       <c r="J92" t="s">
         <v>22</v>
       </c>
       <c r="K92" t="s">
-        <v>22</v>
+        <v>378</v>
       </c>
       <c r="L92" t="s">
-        <v>407</v>
+        <v>256</v>
       </c>
       <c r="M92" t="s">
-        <v>50</v>
-      </c>
-      <c r="N92" t="s">
-        <v>423</v>
+        <v>41</v>
       </c>
       <c r="O92" t="s">
         <v>22</v>
@@ -7186,27 +6719,27 @@
         <v>22</v>
       </c>
       <c r="R92" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S92" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="93" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>424</v>
+        <v>268</v>
       </c>
       <c r="C93" t="s">
-        <v>290</v>
+        <v>171</v>
       </c>
       <c r="D93" t="s">
-        <v>425</v>
+        <v>269</v>
       </c>
       <c r="E93" t="s">
-        <v>426</v>
+        <v>270</v>
       </c>
       <c r="F93" t="s">
         <v>22</v>
@@ -7218,22 +6751,19 @@
         <v>22</v>
       </c>
       <c r="I93" t="s">
-        <v>427</v>
+        <v>271</v>
       </c>
       <c r="J93" t="s">
         <v>22</v>
       </c>
       <c r="K93" t="s">
-        <v>22</v>
+        <v>379</v>
       </c>
       <c r="L93" t="s">
-        <v>428</v>
+        <v>272</v>
       </c>
       <c r="M93" t="s">
-        <v>50</v>
-      </c>
-      <c r="N93" t="s">
-        <v>429</v>
+        <v>41</v>
       </c>
       <c r="O93" t="s">
         <v>22</v>
@@ -7245,27 +6775,27 @@
         <v>22</v>
       </c>
       <c r="R93" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S93" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>430</v>
+        <v>273</v>
       </c>
       <c r="C94" t="s">
         <v>20</v>
       </c>
       <c r="D94" t="s">
-        <v>335</v>
+        <v>200</v>
       </c>
       <c r="E94" t="s">
-        <v>431</v>
+        <v>274</v>
       </c>
       <c r="F94" t="s">
         <v>22</v>
@@ -7277,22 +6807,19 @@
         <v>22</v>
       </c>
       <c r="I94" t="s">
-        <v>432</v>
+        <v>275</v>
       </c>
       <c r="J94" t="s">
         <v>22</v>
       </c>
       <c r="K94" t="s">
-        <v>22</v>
+        <v>380</v>
       </c>
       <c r="L94" t="s">
         <v>22</v>
       </c>
       <c r="M94" t="s">
-        <v>61</v>
-      </c>
-      <c r="N94" t="s">
-        <v>433</v>
+        <v>48</v>
       </c>
       <c r="O94" t="s">
         <v>22</v>
@@ -7304,27 +6831,27 @@
         <v>22</v>
       </c>
       <c r="R94" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S94" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="95" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>434</v>
+        <v>276</v>
       </c>
       <c r="C95" t="s">
-        <v>245</v>
+        <v>146</v>
       </c>
       <c r="D95" t="s">
-        <v>435</v>
+        <v>277</v>
       </c>
       <c r="E95" t="s">
-        <v>436</v>
+        <v>278</v>
       </c>
       <c r="F95" t="s">
         <v>22</v>
@@ -7336,22 +6863,19 @@
         <v>22</v>
       </c>
       <c r="I95" t="s">
-        <v>437</v>
+        <v>279</v>
       </c>
       <c r="J95" t="s">
         <v>22</v>
       </c>
       <c r="K95" t="s">
-        <v>22</v>
+        <v>381</v>
       </c>
       <c r="L95" t="s">
-        <v>438</v>
+        <v>280</v>
       </c>
       <c r="M95" t="s">
-        <v>50</v>
-      </c>
-      <c r="N95" t="s">
-        <v>439</v>
+        <v>41</v>
       </c>
       <c r="O95" t="s">
         <v>22</v>
@@ -7363,27 +6887,27 @@
         <v>22</v>
       </c>
       <c r="R95" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S95" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>440</v>
+        <v>281</v>
       </c>
       <c r="C96" t="s">
-        <v>290</v>
+        <v>171</v>
       </c>
       <c r="D96" t="s">
-        <v>291</v>
+        <v>172</v>
       </c>
       <c r="E96" t="s">
-        <v>343</v>
+        <v>206</v>
       </c>
       <c r="F96" t="s">
         <v>22</v>
@@ -7395,22 +6919,19 @@
         <v>22</v>
       </c>
       <c r="I96" t="s">
-        <v>441</v>
+        <v>282</v>
       </c>
       <c r="J96" t="s">
         <v>22</v>
       </c>
       <c r="K96" t="s">
-        <v>22</v>
+        <v>382</v>
       </c>
       <c r="L96" t="s">
-        <v>442</v>
+        <v>283</v>
       </c>
       <c r="M96" t="s">
-        <v>25</v>
-      </c>
-      <c r="N96" t="s">
-        <v>443</v>
+        <v>24</v>
       </c>
       <c r="O96" t="s">
         <v>22</v>
@@ -7422,27 +6943,27 @@
         <v>22</v>
       </c>
       <c r="R96" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S96" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>444</v>
+        <v>284</v>
       </c>
       <c r="C97" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D97" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E97" t="s">
-        <v>445</v>
+        <v>285</v>
       </c>
       <c r="F97" t="s">
         <v>22</v>
@@ -7454,22 +6975,19 @@
         <v>22</v>
       </c>
       <c r="I97" t="s">
-        <v>446</v>
+        <v>286</v>
       </c>
       <c r="J97" t="s">
         <v>22</v>
       </c>
       <c r="K97" t="s">
-        <v>22</v>
+        <v>383</v>
       </c>
       <c r="L97" t="s">
-        <v>447</v>
+        <v>287</v>
       </c>
       <c r="M97" t="s">
-        <v>25</v>
-      </c>
-      <c r="N97" t="s">
-        <v>448</v>
+        <v>24</v>
       </c>
       <c r="O97" t="s">
         <v>22</v>
@@ -7481,26 +6999,17 @@
         <v>22</v>
       </c>
       <c r="R97" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S97" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="99" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="100" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>450</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:S100" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:S1 A98:S98 A2:J2 L2:M2 A3:J3 L3:M3 A4:J97 L4:M97 O2:S2 O3:S3 O4:S97" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>